--- a/data/inflation/Inflation.xlsx
+++ b/data/inflation/Inflation.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,11 @@
           <t>Infl-Hous</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Z-Score</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -573,6 +578,7 @@
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -631,6 +637,9 @@
       <c r="R3" t="n">
         <v>0.0868422318976</v>
       </c>
+      <c r="S3" t="n">
+        <v>1.406043641981953</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -689,6 +698,9 @@
       <c r="R4" t="n">
         <v>0.08524223189760001</v>
       </c>
+      <c r="S4" t="n">
+        <v>1.361059552491529</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -747,6 +759,9 @@
       <c r="R5" t="n">
         <v>0.1054422318976</v>
       </c>
+      <c r="S5" t="n">
+        <v>1.928983682308137</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -805,6 +820,9 @@
       <c r="R6" t="n">
         <v>0.0210422318976</v>
       </c>
+      <c r="S6" t="n">
+        <v>-0.4439270383117535</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -863,6 +881,9 @@
       <c r="R7" t="n">
         <v>0.0362422318976</v>
       </c>
+      <c r="S7" t="n">
+        <v>-0.01657818815272108</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -921,6 +942,9 @@
       <c r="R8" t="n">
         <v>0.0457422318976</v>
       </c>
+      <c r="S8" t="n">
+        <v>0.2505148431966741</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -979,6 +1003,9 @@
       <c r="R9" t="n">
         <v>0.0174422318976</v>
       </c>
+      <c r="S9" t="n">
+        <v>-0.5451412396652087</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1037,6 +1064,9 @@
       <c r="R10" t="n">
         <v>0.0002422318976000001</v>
       </c>
+      <c r="S10" t="n">
+        <v>-1.028720201687272</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1095,6 +1125,9 @@
       <c r="R11" t="n">
         <v>0.0258422318976</v>
       </c>
+      <c r="S11" t="n">
+        <v>-0.3089747698404801</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1153,6 +1186,9 @@
       <c r="R12" t="n">
         <v>0.0179422318976</v>
       </c>
+      <c r="S12" t="n">
+        <v>-0.531083711699451</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1211,6 +1247,9 @@
       <c r="R13" t="n">
         <v>0.0246422318976</v>
       </c>
+      <c r="S13" t="n">
+        <v>-0.3427128369582985</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1269,6 +1308,9 @@
       <c r="R14" t="n">
         <v>0.0265422318976</v>
       </c>
+      <c r="S14" t="n">
+        <v>-0.2892942306884194</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1327,6 +1369,9 @@
       <c r="R15" t="n">
         <v>0.0624422318976</v>
       </c>
+      <c r="S15" t="n">
+        <v>0.7200362772529796</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1385,6 +1430,9 @@
       <c r="R16" t="n">
         <v>0.0097422318976</v>
       </c>
+      <c r="S16" t="n">
+        <v>-0.7616271703378764</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1443,6 +1491,9 @@
       <c r="R17" t="n">
         <v>0.0130422318976</v>
       </c>
+      <c r="S17" t="n">
+        <v>-0.6688474857638758</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1501,6 +1552,9 @@
       <c r="R18" t="n">
         <v>0.0179422318976</v>
       </c>
+      <c r="S18" t="n">
+        <v>-0.531083711699451</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1559,6 +1613,9 @@
       <c r="R19" t="n">
         <v>0.0313422318976</v>
       </c>
+      <c r="S19" t="n">
+        <v>-0.1543419622171461</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1617,6 +1674,9 @@
       <c r="R20" t="n">
         <v>0.0132422318976</v>
       </c>
+      <c r="S20" t="n">
+        <v>-0.6632244745775728</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1675,6 +1735,9 @@
       <c r="R21" t="n">
         <v>0.0030422318976</v>
       </c>
+      <c r="S21" t="n">
+        <v>-0.9499980450790287</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1733,6 +1796,9 @@
       <c r="R22" t="n">
         <v>0.0019422318976</v>
       </c>
+      <c r="S22" t="n">
+        <v>-0.9809246066036957</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1791,6 +1857,9 @@
       <c r="R23" t="n">
         <v>0.0056422318976</v>
       </c>
+      <c r="S23" t="n">
+        <v>-0.8768988996570891</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -1849,6 +1918,9 @@
       <c r="R24" t="n">
         <v>0.0226422318976</v>
       </c>
+      <c r="S24" t="n">
+        <v>-0.3989429488213291</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -1907,6 +1979,9 @@
       <c r="R25" t="n">
         <v>0.0201422318976</v>
       </c>
+      <c r="S25" t="n">
+        <v>-0.4692305886501174</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -1965,6 +2040,9 @@
       <c r="R26" t="n">
         <v>0.0276422318976</v>
       </c>
+      <c r="S26" t="n">
+        <v>-0.2583676691637527</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -2023,6 +2101,9 @@
       <c r="R27" t="n">
         <v>0.0311422318976</v>
       </c>
+      <c r="S27" t="n">
+        <v>-0.1599649734034491</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -2081,6 +2162,9 @@
       <c r="R28" t="n">
         <v>0.0371422318976</v>
       </c>
+      <c r="S28" t="n">
+        <v>0.008725362185642623</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -2139,6 +2223,9 @@
       <c r="R29" t="n">
         <v>0.1494422318976</v>
       </c>
+      <c r="S29" t="n">
+        <v>3.16604614329481</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -2197,6 +2284,9 @@
       <c r="R30" t="n">
         <v>0.1051422318976</v>
       </c>
+      <c r="S30" t="n">
+        <v>1.920549165528683</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -2254,6 +2344,9 @@
       </c>
       <c r="R31" t="n">
         <v>0.0232422318976</v>
+      </c>
+      <c r="S31" t="n">
+        <v>-0.3820739152624198</v>
       </c>
     </row>
   </sheetData>

--- a/data/inflation/Inflation.xlsx
+++ b/data/inflation/Inflation.xlsx
@@ -516,12 +516,12 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>Z-Score</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>Infl-Hous</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Z-Score</t>
         </is>
       </c>
     </row>
@@ -635,10 +635,10 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="R3" t="n">
+        <v>1.406043641981953</v>
+      </c>
+      <c r="S3" t="n">
         <v>0.0868422318976</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.406043641981953</v>
       </c>
     </row>
     <row r="4">
@@ -696,10 +696,10 @@
         <v>0.0864</v>
       </c>
       <c r="R4" t="n">
+        <v>1.361059552491529</v>
+      </c>
+      <c r="S4" t="n">
         <v>0.08524223189760001</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.361059552491529</v>
       </c>
     </row>
     <row r="5">
@@ -757,10 +757,10 @@
         <v>0.1066</v>
       </c>
       <c r="R5" t="n">
+        <v>1.928983682308137</v>
+      </c>
+      <c r="S5" t="n">
         <v>0.1054422318976</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.928983682308137</v>
       </c>
     </row>
     <row r="6">
@@ -818,10 +818,10 @@
         <v>0.0222</v>
       </c>
       <c r="R6" t="n">
+        <v>-0.4439270383117535</v>
+      </c>
+      <c r="S6" t="n">
         <v>0.0210422318976</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-0.4439270383117535</v>
       </c>
     </row>
     <row r="7">
@@ -879,10 +879,10 @@
         <v>0.0374</v>
       </c>
       <c r="R7" t="n">
+        <v>-0.01657818815272108</v>
+      </c>
+      <c r="S7" t="n">
         <v>0.0362422318976</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-0.01657818815272108</v>
       </c>
     </row>
     <row r="8">
@@ -940,10 +940,10 @@
         <v>0.0469</v>
       </c>
       <c r="R8" t="n">
+        <v>0.2505148431966741</v>
+      </c>
+      <c r="S8" t="n">
         <v>0.0457422318976</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.2505148431966741</v>
       </c>
     </row>
     <row r="9">
@@ -1001,10 +1001,10 @@
         <v>0.0186</v>
       </c>
       <c r="R9" t="n">
+        <v>-0.5451412396652087</v>
+      </c>
+      <c r="S9" t="n">
         <v>0.0174422318976</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-0.5451412396652087</v>
       </c>
     </row>
     <row r="10">
@@ -1062,10 +1062,10 @@
         <v>0.0014</v>
       </c>
       <c r="R10" t="n">
+        <v>-1.028720201687272</v>
+      </c>
+      <c r="S10" t="n">
         <v>0.0002422318976000001</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-1.028720201687272</v>
       </c>
     </row>
     <row r="11">
@@ -1123,10 +1123,10 @@
         <v>0.027</v>
       </c>
       <c r="R11" t="n">
+        <v>-0.3089747698404801</v>
+      </c>
+      <c r="S11" t="n">
         <v>0.0258422318976</v>
-      </c>
-      <c r="S11" t="n">
-        <v>-0.3089747698404801</v>
       </c>
     </row>
     <row r="12">
@@ -1184,10 +1184,10 @@
         <v>0.0191</v>
       </c>
       <c r="R12" t="n">
+        <v>-0.531083711699451</v>
+      </c>
+      <c r="S12" t="n">
         <v>0.0179422318976</v>
-      </c>
-      <c r="S12" t="n">
-        <v>-0.531083711699451</v>
       </c>
     </row>
     <row r="13">
@@ -1245,10 +1245,10 @@
         <v>0.0258</v>
       </c>
       <c r="R13" t="n">
+        <v>-0.3427128369582985</v>
+      </c>
+      <c r="S13" t="n">
         <v>0.0246422318976</v>
-      </c>
-      <c r="S13" t="n">
-        <v>-0.3427128369582985</v>
       </c>
     </row>
     <row r="14">
@@ -1306,10 +1306,10 @@
         <v>0.0277</v>
       </c>
       <c r="R14" t="n">
+        <v>-0.2892942306884194</v>
+      </c>
+      <c r="S14" t="n">
         <v>0.0265422318976</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-0.2892942306884194</v>
       </c>
     </row>
     <row r="15">
@@ -1367,10 +1367,10 @@
         <v>0.0636</v>
       </c>
       <c r="R15" t="n">
+        <v>0.7200362772529796</v>
+      </c>
+      <c r="S15" t="n">
         <v>0.0624422318976</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.7200362772529796</v>
       </c>
     </row>
     <row r="16">
@@ -1428,10 +1428,10 @@
         <v>0.0109</v>
       </c>
       <c r="R16" t="n">
+        <v>-0.7616271703378764</v>
+      </c>
+      <c r="S16" t="n">
         <v>0.0097422318976</v>
-      </c>
-      <c r="S16" t="n">
-        <v>-0.7616271703378764</v>
       </c>
     </row>
     <row r="17">
@@ -1489,10 +1489,10 @@
         <v>0.0142</v>
       </c>
       <c r="R17" t="n">
+        <v>-0.6688474857638758</v>
+      </c>
+      <c r="S17" t="n">
         <v>0.0130422318976</v>
-      </c>
-      <c r="S17" t="n">
-        <v>-0.6688474857638758</v>
       </c>
     </row>
     <row r="18">
@@ -1550,10 +1550,10 @@
         <v>0.0191</v>
       </c>
       <c r="R18" t="n">
+        <v>-0.531083711699451</v>
+      </c>
+      <c r="S18" t="n">
         <v>0.0179422318976</v>
-      </c>
-      <c r="S18" t="n">
-        <v>-0.531083711699451</v>
       </c>
     </row>
     <row r="19">
@@ -1611,10 +1611,10 @@
         <v>0.0325</v>
       </c>
       <c r="R19" t="n">
+        <v>-0.1543419622171461</v>
+      </c>
+      <c r="S19" t="n">
         <v>0.0313422318976</v>
-      </c>
-      <c r="S19" t="n">
-        <v>-0.1543419622171461</v>
       </c>
     </row>
     <row r="20">
@@ -1672,10 +1672,10 @@
         <v>0.0144</v>
       </c>
       <c r="R20" t="n">
+        <v>-0.6632244745775728</v>
+      </c>
+      <c r="S20" t="n">
         <v>0.0132422318976</v>
-      </c>
-      <c r="S20" t="n">
-        <v>-0.6632244745775728</v>
       </c>
     </row>
     <row r="21">
@@ -1733,10 +1733,10 @@
         <v>0.0042</v>
       </c>
       <c r="R21" t="n">
+        <v>-0.9499980450790287</v>
+      </c>
+      <c r="S21" t="n">
         <v>0.0030422318976</v>
-      </c>
-      <c r="S21" t="n">
-        <v>-0.9499980450790287</v>
       </c>
     </row>
     <row r="22">
@@ -1794,10 +1794,10 @@
         <v>0.0031</v>
       </c>
       <c r="R22" t="n">
+        <v>-0.9809246066036957</v>
+      </c>
+      <c r="S22" t="n">
         <v>0.0019422318976</v>
-      </c>
-      <c r="S22" t="n">
-        <v>-0.9809246066036957</v>
       </c>
     </row>
     <row r="23">
@@ -1855,10 +1855,10 @@
         <v>0.0068</v>
       </c>
       <c r="R23" t="n">
+        <v>-0.8768988996570891</v>
+      </c>
+      <c r="S23" t="n">
         <v>0.0056422318976</v>
-      </c>
-      <c r="S23" t="n">
-        <v>-0.8768988996570891</v>
       </c>
     </row>
     <row r="24">
@@ -1916,10 +1916,10 @@
         <v>0.0238</v>
       </c>
       <c r="R24" t="n">
+        <v>-0.3989429488213291</v>
+      </c>
+      <c r="S24" t="n">
         <v>0.0226422318976</v>
-      </c>
-      <c r="S24" t="n">
-        <v>-0.3989429488213291</v>
       </c>
     </row>
     <row r="25">
@@ -1977,10 +1977,10 @@
         <v>0.0213</v>
       </c>
       <c r="R25" t="n">
+        <v>-0.4692305886501174</v>
+      </c>
+      <c r="S25" t="n">
         <v>0.0201422318976</v>
-      </c>
-      <c r="S25" t="n">
-        <v>-0.4692305886501174</v>
       </c>
     </row>
     <row r="26">
@@ -2038,10 +2038,10 @@
         <v>0.0288</v>
       </c>
       <c r="R26" t="n">
+        <v>-0.2583676691637527</v>
+      </c>
+      <c r="S26" t="n">
         <v>0.0276422318976</v>
-      </c>
-      <c r="S26" t="n">
-        <v>-0.2583676691637527</v>
       </c>
     </row>
     <row r="27">
@@ -2099,10 +2099,10 @@
         <v>0.0323</v>
       </c>
       <c r="R27" t="n">
+        <v>-0.1599649734034491</v>
+      </c>
+      <c r="S27" t="n">
         <v>0.0311422318976</v>
-      </c>
-      <c r="S27" t="n">
-        <v>-0.1599649734034491</v>
       </c>
     </row>
     <row r="28">
@@ -2160,10 +2160,10 @@
         <v>0.0383</v>
       </c>
       <c r="R28" t="n">
+        <v>0.008725362185642623</v>
+      </c>
+      <c r="S28" t="n">
         <v>0.0371422318976</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0.008725362185642623</v>
       </c>
     </row>
     <row r="29">
@@ -2221,10 +2221,10 @@
         <v>0.1506</v>
       </c>
       <c r="R29" t="n">
+        <v>3.16604614329481</v>
+      </c>
+      <c r="S29" t="n">
         <v>0.1494422318976</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.16604614329481</v>
       </c>
     </row>
     <row r="30">
@@ -2282,10 +2282,10 @@
         <v>0.1063</v>
       </c>
       <c r="R30" t="n">
+        <v>1.920549165528683</v>
+      </c>
+      <c r="S30" t="n">
         <v>0.1051422318976</v>
-      </c>
-      <c r="S30" t="n">
-        <v>1.920549165528683</v>
       </c>
     </row>
     <row r="31">
@@ -2343,10 +2343,10 @@
         <v>0.0244</v>
       </c>
       <c r="R31" t="n">
+        <v>-0.3820739152624198</v>
+      </c>
+      <c r="S31" t="n">
         <v>0.0232422318976</v>
-      </c>
-      <c r="S31" t="n">
-        <v>-0.3820739152624198</v>
       </c>
     </row>
   </sheetData>
